--- a/Data/FlightPlan/FPL_18AUG26.xlsx
+++ b/Data/FlightPlan/FPL_18AUG26.xlsx
@@ -557,6 +557,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:44</t>
+  </si>
+  <si>
     <t>08:35</t>
   </si>
   <si>
@@ -587,6 +590,12 @@
     <t>VN-A543</t>
   </si>
   <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>13:30</t>
   </si>
   <si>
@@ -698,9 +707,6 @@
     <t>VN-A552</t>
   </si>
   <si>
-    <t>12:05</t>
-  </si>
-  <si>
     <t>13:45</t>
   </si>
   <si>
@@ -752,252 +758,252 @@
     <t>09:35</t>
   </si>
   <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
     <t>07:25</t>
   </si>
   <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
     <t>12:30</t>
   </si>
   <si>
@@ -1247,7 +1253,7 @@
     <t>Total Record(s): 381</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 17, 2026 22:11</t>
+    <t xml:space="preserve">Generated on  Aug 18, 2026 03:20</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4390,7 +4396,9 @@
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
+      <c t="s" r="M92" s="7">
+        <v>182</v>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c t="s" r="A93" s="6">
@@ -4416,7 +4424,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>108</v>
@@ -4449,10 +4457,10 @@
         <v>63</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4482,7 +4490,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>113</v>
@@ -4518,7 +4526,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4530,7 +4538,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>156</v>
@@ -4551,7 +4559,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4563,7 +4571,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>150</v>
@@ -4584,7 +4592,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4596,7 +4604,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>81</v>
@@ -4617,7 +4625,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4629,7 +4637,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>25</v>
@@ -4650,7 +4658,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4683,7 +4691,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4731,7 +4739,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4748,9 +4756,13 @@
       <c t="s" r="J104" s="7">
         <v>126</v>
       </c>
-      <c r="K104" s="7"/>
+      <c t="s" r="K104" s="7">
+        <v>193</v>
+      </c>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>194</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
@@ -4764,7 +4776,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4776,7 +4788,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>88</v>
@@ -4797,7 +4809,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4812,7 +4824,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4830,7 +4842,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4842,7 +4854,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>77</v>
@@ -4878,22 +4890,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4911,7 +4923,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4944,7 +4956,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4956,7 +4968,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>111</v>
@@ -4977,7 +4989,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4989,7 +5001,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>130</v>
@@ -5010,7 +5022,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5025,7 +5037,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5043,7 +5055,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5055,10 +5067,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5091,7 +5103,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5124,7 +5136,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5136,7 +5148,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>141</v>
@@ -5157,7 +5169,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5169,17 +5181,17 @@
         <v>167</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="K118" s="7">
         <v>131</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5194,7 +5206,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5206,7 +5218,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>19</v>
@@ -5242,7 +5254,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5254,7 +5266,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>127</v>
@@ -5275,7 +5287,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5290,7 +5302,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5308,7 +5320,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5317,13 +5329,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5341,22 +5353,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5401,7 +5413,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>149</v>
@@ -5422,7 +5434,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5434,10 +5446,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5455,7 +5467,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5488,7 +5500,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5500,7 +5512,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>129</v>
@@ -5521,7 +5533,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5536,7 +5548,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5554,7 +5566,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5566,10 +5578,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5602,7 +5614,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5614,10 +5626,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5635,7 +5647,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5668,7 +5680,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5683,7 +5695,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5701,7 +5713,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5713,7 +5725,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>46</v>
@@ -5749,7 +5761,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5764,7 +5776,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5782,7 +5794,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5797,7 +5809,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5815,7 +5827,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5848,7 +5860,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5860,7 +5872,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>72</v>
@@ -5881,7 +5893,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5896,7 +5908,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5929,7 +5941,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5941,10 +5953,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5962,7 +5974,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5995,7 +6007,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6007,10 +6019,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6028,7 +6040,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6061,7 +6073,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6094,7 +6106,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6106,10 +6118,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6142,7 +6154,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6157,7 +6169,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6175,7 +6187,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6187,10 +6199,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6208,7 +6220,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6223,7 +6235,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6237,11 +6249,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6253,10 +6265,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6270,11 +6282,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6283,10 +6295,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>19</v>
@@ -6322,7 +6334,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6334,17 +6346,17 @@
         <v>167</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>247</v>
+        <v>46</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>87</v>
+        <v>236</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6355,11 +6367,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6388,11 +6400,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6401,13 +6413,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6421,23 +6433,23 @@
         <v>5069</v>
       </c>
       <c t="s" r="C160" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>146</v>
@@ -6473,7 +6485,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6485,14 +6497,16 @@
         <v>63</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>159</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
+      <c t="s" r="M162" s="7">
+        <v>253</v>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c t="s" r="A163" s="6">
@@ -6506,7 +6520,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6521,7 +6535,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6539,7 +6553,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6572,7 +6586,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6584,10 +6598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6620,7 +6634,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6653,7 +6667,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6668,7 +6682,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6686,7 +6700,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6719,7 +6733,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6728,13 +6742,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>170</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6752,13 +6766,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>33</v>
@@ -6800,7 +6814,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6809,7 +6823,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>76</v>
@@ -6833,22 +6847,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6866,7 +6880,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6914,7 +6928,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6926,10 +6940,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6947,7 +6961,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6962,7 +6976,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6980,7 +6994,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7013,7 +7027,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7022,10 +7036,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>121</v>
@@ -7046,19 +7060,19 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>123</v>
@@ -7079,7 +7093,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7091,7 +7105,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>146</v>
@@ -7127,7 +7141,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7139,10 +7153,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7160,7 +7174,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7169,7 +7183,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>87</v>
@@ -7193,19 +7207,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>111</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7238,10 +7252,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7259,7 +7273,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7271,10 +7285,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7307,7 +7321,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7316,13 +7330,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7340,22 +7354,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7373,7 +7387,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7382,10 +7396,10 @@
         <v>112</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>55</v>
@@ -7406,19 +7420,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>154</v>
@@ -7454,7 +7468,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7466,7 +7480,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>80</v>
@@ -7487,7 +7501,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7499,7 +7513,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>109</v>
@@ -7520,7 +7534,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7568,7 +7582,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7601,7 +7615,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7613,10 +7627,10 @@
         <v>107</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7634,7 +7648,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7649,7 +7663,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7667,7 +7681,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7700,7 +7714,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7712,7 +7726,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>139</v>
@@ -7733,7 +7747,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7745,10 +7759,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7766,7 +7780,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7778,7 +7792,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>145</v>
@@ -7814,7 +7828,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7829,7 +7843,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7847,7 +7861,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7859,10 +7873,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7880,7 +7894,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7889,13 +7903,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7913,22 +7927,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7961,7 +7975,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7976,7 +7990,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="K212" s="7">
         <v>77</v>
@@ -7998,7 +8012,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8010,17 +8024,17 @@
         <v>33</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="K213" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8035,7 +8049,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8047,7 +8061,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>120</v>
@@ -8068,7 +8082,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8080,7 +8094,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>178</v>
@@ -8101,7 +8115,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8113,10 +8127,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8134,7 +8148,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8146,10 +8160,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8182,7 +8196,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8194,7 +8208,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>166</v>
@@ -8215,7 +8229,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8224,10 +8238,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>119</v>
@@ -8248,13 +8262,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
@@ -8281,7 +8295,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8296,7 +8310,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8314,7 +8328,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8329,7 +8343,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8347,7 +8361,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8362,7 +8376,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8380,7 +8394,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8392,10 +8406,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8428,7 +8442,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8440,7 +8454,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>77</v>
@@ -8457,11 +8471,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C228" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8470,13 +8484,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8490,17 +8504,17 @@
         <v>8521</v>
       </c>
       <c t="s" r="C229" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>112</v>
@@ -8527,7 +8541,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8542,7 +8556,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8575,7 +8589,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8587,7 +8601,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>149</v>
@@ -8608,7 +8622,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8620,10 +8634,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8641,7 +8655,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8653,7 +8667,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>23</v>
@@ -8674,7 +8688,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8689,7 +8703,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8707,7 +8721,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8716,7 +8730,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>121</v>
@@ -8725,11 +8739,11 @@
         <v>137</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -8744,13 +8758,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>33</v>
@@ -8759,14 +8773,14 @@
         <v>141</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="K237" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -8796,7 +8810,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8808,10 +8822,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8829,7 +8843,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8841,7 +8855,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>150</v>
@@ -8862,7 +8876,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8874,10 +8888,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8895,7 +8909,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8907,7 +8921,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>69</v>
@@ -8928,7 +8942,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8961,7 +8975,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8973,10 +8987,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9009,7 +9023,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9024,7 +9038,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9042,7 +9056,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9075,7 +9089,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9090,7 +9104,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9123,7 +9137,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9156,7 +9170,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9168,10 +9182,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9189,7 +9203,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9198,13 +9212,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9222,19 +9236,19 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>124</v>
@@ -9255,7 +9269,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9267,7 +9281,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>162</v>
@@ -9288,7 +9302,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9300,10 +9314,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9336,7 +9350,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9351,7 +9365,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9369,7 +9383,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9378,10 +9392,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>91</v>
@@ -9402,22 +9416,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9450,7 +9464,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9465,7 +9479,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9483,7 +9497,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9492,13 +9506,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9516,22 +9530,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9549,7 +9563,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9561,7 +9575,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>113</v>
@@ -9582,7 +9596,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9591,13 +9605,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9615,22 +9629,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9663,7 +9677,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9696,7 +9710,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9708,7 +9722,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>149</v>
@@ -9729,7 +9743,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9744,7 +9758,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9762,7 +9776,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9774,7 +9788,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>35</v>
@@ -9795,7 +9809,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9807,10 +9821,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9828,7 +9842,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9840,7 +9854,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>37</v>
@@ -9876,7 +9890,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9891,7 +9905,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9909,7 +9923,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9921,7 +9935,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>21</v>
@@ -9942,7 +9956,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9951,13 +9965,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9975,13 +9989,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>16</v>
@@ -10008,7 +10022,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10023,7 +10037,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10041,7 +10055,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10056,7 +10070,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10089,7 +10103,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10101,7 +10115,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>181</v>
@@ -10122,7 +10136,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10134,10 +10148,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10155,7 +10169,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10170,7 +10184,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10188,7 +10202,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10221,7 +10235,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10233,7 +10247,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>141</v>
@@ -10254,7 +10268,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10269,7 +10283,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10302,7 +10316,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10317,7 +10331,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10335,7 +10349,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10350,7 +10364,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10368,7 +10382,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10380,7 +10394,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>160</v>
@@ -10401,7 +10415,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10413,10 +10427,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10434,7 +10448,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10443,10 +10457,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>143</v>
@@ -10467,22 +10481,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10515,7 +10529,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10524,13 +10538,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10548,22 +10562,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10581,7 +10595,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10590,10 +10604,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>79</v>
@@ -10614,13 +10628,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -10629,7 +10643,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10647,7 +10661,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10656,13 +10670,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10680,19 +10694,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>44</v>
@@ -10728,7 +10742,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10743,7 +10757,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10761,7 +10775,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10773,7 +10787,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>41</v>
@@ -10783,7 +10797,7 @@
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -10813,7 +10827,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10828,7 +10842,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10846,7 +10860,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10879,7 +10893,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10891,10 +10905,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10912,7 +10926,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10921,7 +10935,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>35</v>
@@ -10945,13 +10959,13 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>33</v>
@@ -10993,7 +11007,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11008,7 +11022,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11026,7 +11040,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11041,7 +11055,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11059,7 +11073,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11092,7 +11106,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11125,7 +11139,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11158,7 +11172,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11170,7 +11184,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>100</v>
@@ -11191,7 +11205,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11203,10 +11217,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11224,7 +11238,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11236,7 +11250,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>18</v>
@@ -11272,7 +11286,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11281,13 +11295,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11305,22 +11319,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11338,7 +11352,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11371,7 +11385,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11383,7 +11397,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>124</v>
@@ -11419,7 +11433,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11428,13 +11442,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11452,22 +11466,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11485,7 +11499,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11497,7 +11511,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>23</v>
@@ -11518,7 +11532,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11533,7 +11547,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11551,7 +11565,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11584,7 +11598,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11599,7 +11613,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11632,7 +11646,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11644,10 +11658,10 @@
         <v>107</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11665,7 +11679,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11677,7 +11691,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>117</v>
@@ -11698,7 +11712,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11731,7 +11745,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11743,7 +11757,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>131</v>
@@ -11764,7 +11778,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11776,7 +11790,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>162</v>
@@ -11812,7 +11826,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11821,13 +11835,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11845,13 +11859,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
@@ -11878,7 +11892,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11893,7 +11907,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11926,7 +11940,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11935,13 +11949,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11959,13 +11973,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>33</v>
@@ -11992,7 +12006,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12001,13 +12015,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12025,13 +12039,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>33</v>
@@ -12040,7 +12054,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12058,7 +12072,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12070,7 +12084,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>129</v>
@@ -12091,7 +12105,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12124,7 +12138,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12136,10 +12150,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12172,7 +12186,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12181,10 +12195,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>96</v>
@@ -12205,13 +12219,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>33</v>
@@ -12238,7 +12252,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12271,7 +12285,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12280,7 +12294,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>68</v>
@@ -12304,13 +12318,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>16</v>
@@ -12337,7 +12351,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12352,7 +12366,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12370,7 +12384,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12382,10 +12396,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12418,7 +12432,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12430,10 +12444,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12451,7 +12465,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12460,10 +12474,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>117</v>
@@ -12484,22 +12498,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12517,7 +12531,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12529,7 +12543,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>164</v>
@@ -12565,7 +12579,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12574,13 +12588,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12598,19 +12612,19 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>65</v>
@@ -12631,7 +12645,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12643,10 +12657,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12664,7 +12678,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12676,7 +12690,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>120</v>
@@ -12697,7 +12711,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12706,10 +12720,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>177</v>
@@ -12730,13 +12744,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>16</v>
@@ -12745,7 +12759,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12778,7 +12792,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12790,10 +12804,10 @@
         <v>63</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12811,7 +12825,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12823,10 +12837,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12859,7 +12873,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12871,7 +12885,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>85</v>
@@ -12892,7 +12906,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12904,10 +12918,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12925,7 +12939,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12937,7 +12951,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>120</v>
@@ -12958,7 +12972,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -12987,11 +13001,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C378" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13000,13 +13014,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13020,26 +13034,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C379" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13072,13 +13086,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>33</v>
@@ -13087,7 +13101,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13105,7 +13119,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13114,10 +13128,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>69</v>
@@ -13138,13 +13152,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>33</v>
@@ -13153,7 +13167,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13171,7 +13185,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13180,13 +13194,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13204,13 +13218,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>33</v>
@@ -13219,7 +13233,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13252,7 +13266,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13264,7 +13278,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>64</v>
@@ -13285,7 +13299,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13297,7 +13311,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>165</v>
@@ -13318,7 +13332,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13333,7 +13347,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13351,7 +13365,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13363,7 +13377,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>35</v>
@@ -13384,7 +13398,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13396,7 +13410,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>70</v>
@@ -13417,7 +13431,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13450,7 +13464,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13462,10 +13476,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13483,7 +13497,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13495,10 +13509,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13531,7 +13545,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13543,10 +13557,10 @@
         <v>175</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13564,7 +13578,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13576,7 +13590,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>176</v>
@@ -13597,7 +13611,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13609,10 +13623,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13630,7 +13644,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13639,10 +13653,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>177</v>
@@ -13663,13 +13677,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>16</v>
@@ -13696,7 +13710,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13708,10 +13722,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13729,7 +13743,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13741,10 +13755,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13777,7 +13791,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13789,7 +13803,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>156</v>
@@ -13810,7 +13824,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13822,10 +13836,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13843,7 +13857,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13855,7 +13869,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>21</v>
@@ -13876,7 +13890,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13888,10 +13902,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13909,7 +13923,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13921,10 +13935,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13942,7 +13956,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13990,7 +14004,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14023,7 +14037,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14035,10 +14049,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14071,7 +14085,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14086,7 +14100,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14104,7 +14118,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14116,7 +14130,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>98</v>
@@ -14137,7 +14151,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14149,7 +14163,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>127</v>
@@ -14170,7 +14184,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14182,10 +14196,10 @@
         <v>63</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14203,7 +14217,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14236,7 +14250,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14251,7 +14265,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14269,7 +14283,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14317,7 +14331,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14350,7 +14364,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14362,13 +14376,13 @@
         <v>175</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>23</v>
       </c>
       <c t="s" r="K423" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
@@ -14387,7 +14401,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14402,10 +14416,10 @@
         <v>50</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="K424" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
@@ -14439,7 +14453,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14451,7 +14465,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>106</v>
@@ -14472,7 +14486,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14481,10 +14495,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>50</v>
@@ -14505,13 +14519,13 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>33</v>
@@ -14538,7 +14552,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14571,7 +14585,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14583,7 +14597,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>154</v>
@@ -14619,7 +14633,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14652,7 +14666,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -14664,10 +14678,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14685,7 +14699,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14697,10 +14711,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14718,7 +14732,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -14751,7 +14765,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14763,10 +14777,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14784,7 +14798,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14796,7 +14810,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>26</v>
@@ -14817,7 +14831,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14832,7 +14846,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14850,7 +14864,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14862,10 +14876,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14883,7 +14897,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -14895,10 +14909,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14931,7 +14945,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -14943,10 +14957,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14964,7 +14978,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -14976,10 +14990,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14997,7 +15011,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15009,7 +15023,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>79</v>
@@ -15030,7 +15044,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15063,7 +15077,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15075,10 +15089,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15096,7 +15110,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15137,14 +15151,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B449" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="C449" s="7">
         <v>14</v>
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -15153,16 +15167,16 @@
         <v>112</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K449" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
@@ -15181,19 +15195,19 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>181</v>
@@ -15229,7 +15243,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15238,13 +15252,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15277,7 +15291,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15286,10 +15300,10 @@
         <v>167</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>123</v>
@@ -15310,13 +15324,13 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>167</v>
@@ -15358,22 +15372,22 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>167</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15391,7 +15405,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15400,13 +15414,13 @@
         <v>167</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15439,7 +15453,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15448,10 +15462,10 @@
         <v>167</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>55</v>
@@ -15472,13 +15486,13 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>167</v>
@@ -15487,7 +15501,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15516,17 +15530,17 @@
         <v>30</v>
       </c>
       <c t="s" r="C463" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>112</v>
@@ -15535,7 +15549,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15568,7 +15582,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
@@ -15577,7 +15591,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>65</v>
@@ -15601,22 +15615,22 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15624,7 +15638,7 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c t="s" r="A467" s="9">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
@@ -15644,7 +15658,7 @@
     <row r="468" ht="65.25" customHeight="1"/>
     <row r="469" ht="16.5" customHeight="1">
       <c t="s" r="A469" s="10">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B469" s="10"/>
       <c r="C469" s="10"/>
@@ -15657,7 +15671,7 @@
       <c r="J469" s="10"/>
       <c r="K469" s="10"/>
       <c t="s" r="L469" s="11">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M469" s="11"/>
       <c r="N469" s="11"/>
